--- a/Enphase_con_IA.xlsx
+++ b/Enphase_con_IA.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jean_Valjean\CASAS\CASA_Sevilla\Fotovoltaica\DATOS_DETALLADOS\Datos_Mensuales\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nalanuka\Desktop\dashboard-enphase\Enphase_Dashboard_3_0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEFCC87B-99F7-486A-B4F8-BBB730047E37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A90717A4-A7F7-4944-A2A9-7E69BF178DC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{45146E1A-4DD6-4F9D-9A6F-E552DB99F2EA}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="164">
   <si>
     <t>Mes del informe</t>
   </si>
@@ -518,6 +518,15 @@
   </si>
   <si>
     <t>Versión gratuita</t>
+  </si>
+  <si>
+    <t>999 kWh</t>
+  </si>
+  <si>
+    <t>99 kWh (Imp: 99 kWh, Exp: 99 kWh)</t>
+  </si>
+  <si>
+    <t>99 kWh</t>
   </si>
 </sst>
 </file>
@@ -875,7 +884,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BF96B80-7DE3-4FDC-A8C2-EB98A70702AC}">
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="5" max="5" width="37.21875" customWidth="1"/>
@@ -1836,6 +1845,35 @@
       </c>
       <c r="I33" t="s">
         <v>158</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>46235</v>
+      </c>
+      <c r="B34" s="2">
+        <v>46277</v>
+      </c>
+      <c r="C34" t="s">
+        <v>161</v>
+      </c>
+      <c r="D34" t="s">
+        <v>161</v>
+      </c>
+      <c r="E34" t="s">
+        <v>162</v>
+      </c>
+      <c r="F34" s="3">
+        <v>46246</v>
+      </c>
+      <c r="G34" t="s">
+        <v>163</v>
+      </c>
+      <c r="H34" s="3">
+        <v>46246</v>
+      </c>
+      <c r="I34" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/Enphase_con_IA.xlsx
+++ b/Enphase_con_IA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nalanuka\Desktop\dashboard-enphase\Enphase_Dashboard_3_0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A90717A4-A7F7-4944-A2A9-7E69BF178DC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7B778A5-8599-42E5-A8D9-6E2EB8D69517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{45146E1A-4DD6-4F9D-9A6F-E552DB99F2EA}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="161">
   <si>
     <t>Mes del informe</t>
   </si>
@@ -518,15 +518,6 @@
   </si>
   <si>
     <t>Versión gratuita</t>
-  </si>
-  <si>
-    <t>999 kWh</t>
-  </si>
-  <si>
-    <t>99 kWh (Imp: 99 kWh, Exp: 99 kWh)</t>
-  </si>
-  <si>
-    <t>99 kWh</t>
   </si>
 </sst>
 </file>
@@ -1852,28 +1843,28 @@
         <v>46235</v>
       </c>
       <c r="B34" s="2">
-        <v>46277</v>
+        <v>46274</v>
       </c>
       <c r="C34" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D34" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="E34" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="F34" s="3">
         <v>46246</v>
       </c>
       <c r="G34" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="H34" s="3">
         <v>46246</v>
       </c>
       <c r="I34" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
